--- a/docs/data/predictions/2026-04-22_HV.xlsx
+++ b/docs/data/predictions/2026-04-22_HV.xlsx
@@ -539,12 +539,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="n">
-        <v>1</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -556,8 +560,10 @@
           <t>NEBRASKAN</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -574,47 +580,79 @@
           <t>8/4/6/2/7/3</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="K2" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>8.434782608695652</v>
-      </c>
-      <c r="P2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5.8883</v>
-      </c>
-      <c r="R2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4.4</v>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>8.434782608695652</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>5.8883</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
       </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="n">
-        <v>2</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -626,8 +664,10 @@
           <t>CONCORDE STAR</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>5</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -644,47 +684,79 @@
           <t>8/7/7/2/1/9</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="K3" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="L3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>8.434782608695652</v>
-      </c>
-      <c r="P3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5.6307</v>
-      </c>
-      <c r="R3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5.6</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5.48</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>8.434782608695652</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5.6307</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
       </c>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="n">
-        <v>3</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -696,8 +768,10 @@
           <t>HAPPY BOYS</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>7</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -714,47 +788,79 @@
           <t>6/9/3/3/5/6</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="K4" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="L4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>8.043478260869566</v>
-      </c>
-      <c r="P4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5.5147</v>
-      </c>
-      <c r="R4" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6.3</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5.38</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6.65</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>8.043478260869566</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5.5147</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
       </c>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="n">
-        <v>4</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -766,8 +872,10 @@
           <t>TEAM HAPPY</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>4</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -784,47 +892,79 @@
           <t>4/11/9/5/8/2</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>4.913043478260869</v>
-      </c>
-      <c r="P5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="R5" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="S5" t="n">
-        <v>8.6</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4.67</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>4.913043478260869</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5.21</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
       </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="n">
-        <v>1</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -836,8 +976,10 @@
           <t>DOUBLE BINGO</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>4</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -854,47 +996,79 @@
           <t>2/4/8/5/1/3</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>7.631578947368421</v>
-      </c>
-      <c r="P6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5.9995</v>
-      </c>
-      <c r="R6" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.6</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>7.631578947368421</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5.9995</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
       </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="n">
-        <v>2</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -906,8 +1080,10 @@
           <t>PODIUM</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -924,47 +1100,79 @@
           <t>7/6/4/8/4/1</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="K7" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>7.631578947368421</v>
-      </c>
-      <c r="P7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5.856</v>
-      </c>
-      <c r="R7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5.3</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6.05</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>7.631578947368421</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5.856</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>15.9</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
       </c>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="n">
-        <v>3</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -976,8 +1184,10 @@
           <t>DOUBLE SHOW</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>6</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -994,47 +1204,79 @@
           <t>3/12/2/1/12/5</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7</v>
-      </c>
-      <c r="L8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>7.157894736842105</v>
-      </c>
-      <c r="P8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5.4648</v>
-      </c>
-      <c r="R8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="S8" t="n">
-        <v>7.9</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5.33</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>7.157894736842105</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5.4648</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>10.8</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
       </c>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="n">
-        <v>4</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1046,8 +1288,10 @@
           <t>TELECOM POWER</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>10</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1064,47 +1308,79 @@
           <t>7/5/2/3/6/8</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>9.526315789473685</v>
-      </c>
-      <c r="P9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5.3929</v>
-      </c>
-      <c r="R9" t="n">
-        <v>10</v>
-      </c>
-      <c r="S9" t="n">
-        <v>8.5</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>9.526315789473685</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5.3929</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
       </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>3</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="n">
-        <v>1</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1116,8 +1392,10 @@
           <t>GLORIOUS JOURNEY</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>5</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1134,47 +1412,79 @@
           <t>9/2/4/7/2/1</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="K10" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>10</v>
-      </c>
-      <c r="P10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.2629</v>
-      </c>
-      <c r="R10" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.3</v>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>6.2629</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>25.9</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
       </c>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>3</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="n">
-        <v>2</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1186,8 +1496,10 @@
           <t>APOLAR FIGHTER</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>10</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1204,47 +1516,79 @@
           <t>8/9/14/1/2/1</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.6014</v>
-      </c>
-      <c r="R11" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="S11" t="n">
-        <v>6.3</v>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>7.33</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5.6014</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
       </c>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>3</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="n">
-        <v>3</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1256,8 +1600,10 @@
           <t>FORTUNE STAR</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>6</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1274,47 +1620,79 @@
           <t>4/6/7/4/1/12</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>7</v>
-      </c>
-      <c r="P12" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.327</v>
-      </c>
-      <c r="R12" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>8.300000000000001</v>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>5.327</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
       </c>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="n">
-        <v>4</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1326,8 +1704,10 @@
           <t>OUR LUCKY GLORY</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>12</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1344,47 +1724,79 @@
           <t>3/10/3/3/3/4</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5.3088</v>
-      </c>
-      <c r="R13" t="n">
-        <v>10</v>
-      </c>
-      <c r="S13" t="n">
-        <v>8.5</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>6.76</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>5.3088</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
       </c>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>4</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="n">
-        <v>1</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1396,8 +1808,10 @@
           <t>VIGOR EYE</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>2</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1414,47 +1828,79 @@
           <t>2/9/3/4/3</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="K14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="P14" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>5.8919</v>
-      </c>
-      <c r="R14" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4.3</v>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6.73</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>5.8919</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
       </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>4</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="n">
-        <v>2</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1466,8 +1912,10 @@
           <t>LUCKY MCQUEEN</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>12</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1484,47 +1932,79 @@
           <t>4/1/4/3/8/2</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P15" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5.5916</v>
-      </c>
-      <c r="R15" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5.8</v>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>5.5916</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
       </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>4</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="n">
-        <v>3</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1536,8 +2016,10 @@
           <t>JOLLY COMPANION</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>4</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1554,47 +2036,79 @@
           <t>5/5/9/2/1/9</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="K16" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="P16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5.5321</v>
-      </c>
-      <c r="R16" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="S16" t="n">
-        <v>6.1</v>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>5.67</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>5.5321</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>13.9</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
       </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="n">
-        <v>4</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1606,8 +2120,10 @@
           <t>LEADING AGILITY</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>6</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1624,47 +2140,79 @@
           <t>4/9/7/3</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>7</v>
-      </c>
-      <c r="L17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P17" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5.215</v>
-      </c>
-      <c r="R17" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>8.4</v>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>5.215</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
       </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>5</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" t="n">
-        <v>1</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1676,8 +2224,10 @@
           <t>SPEEDY SMARTIE</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>10</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1694,47 +2244,79 @@
           <t>2/2/1/2/4/1</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>10</v>
-      </c>
-      <c r="P18" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6.4778</v>
-      </c>
-      <c r="R18" t="n">
-        <v>22</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.9</v>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>8.71</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>6.4778</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>5</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="n">
-        <v>2</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1746,8 +2328,10 @@
           <t>SUPER LOVE</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>5</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1764,47 +2348,79 @@
           <t>14/5/14/8/1/2</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>6</v>
-      </c>
-      <c r="K19" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="L19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>9</v>
-      </c>
-      <c r="P19" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.8065</v>
-      </c>
-      <c r="R19" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="S19" t="n">
-        <v>7.6</v>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>5.8065</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
       </c>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>5</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="n">
-        <v>3</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1816,8 +2432,10 @@
           <t>KING OBERON</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>6</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1834,47 +2452,79 @@
           <t>9/10/13/7/1/1</t>
         </is>
       </c>
-      <c r="J20" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="K20" t="n">
-        <v>7</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>8</v>
-      </c>
-      <c r="P20" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5.7442</v>
-      </c>
-      <c r="R20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="S20" t="n">
-        <v>8.1</v>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>6.14</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>5.7442</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
       </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>5</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="n">
-        <v>4</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1886,8 +2536,10 @@
           <t>WINNING MONEY</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>9</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1904,47 +2556,79 @@
           <t>7/1/3/3/2/11</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="K21" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="L21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P21" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.6287</v>
-      </c>
-      <c r="R21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>9</v>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>6.19</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>5.6287</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>6</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="n">
-        <v>1</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1956,8 +2640,10 @@
           <t>HEALTHY HEALTHY</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>2</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1974,47 +2660,79 @@
           <t>10/2/3/4/2/5</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="K22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>10</v>
-      </c>
-      <c r="P22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.1838</v>
-      </c>
-      <c r="R22" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4</v>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>6.76</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>6.1838</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>21.3</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>6</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" t="n">
-        <v>2</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2026,8 +2744,10 @@
           <t>GRAND NOVA</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>1</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2044,47 +2764,79 @@
           <t>4/3/9/4/3/6</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="K23" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>5.6161</v>
-      </c>
-      <c r="R23" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>7</v>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>5.52</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>5.6161</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>6</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" t="n">
-        <v>3</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2096,8 +2848,10 @@
           <t>DAY DAY VICTORY</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>6</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2114,47 +2868,79 @@
           <t>4/5/8/5/7/1</t>
         </is>
       </c>
-      <c r="J24" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="K24" t="n">
-        <v>7</v>
-      </c>
-      <c r="L24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="P24" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5.5356</v>
-      </c>
-      <c r="R24" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="S24" t="n">
-        <v>7.6</v>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>5.5356</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
       </c>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>6</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="n">
-        <v>4</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2166,8 +2952,10 @@
           <t>KING PROFIT</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>12</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2184,47 +2972,79 @@
           <t>2/2/5/4/5/6</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="P25" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5.4789</v>
-      </c>
-      <c r="R25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>8.1</v>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>5.48</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>9.55</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>5.4789</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
       </c>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>7</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="n">
-        <v>1</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2236,8 +3056,10 @@
           <t>BUNTA BABY</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>11</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2254,47 +3076,79 @@
           <t>1/1/3/1/2/3</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="K26" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="L26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>5</v>
-      </c>
-      <c r="P26" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6.1495</v>
-      </c>
-      <c r="R26" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S26" t="n">
-        <v>4.1</v>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>6.1495</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>7</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
-        <v>2</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2306,8 +3160,10 @@
           <t>SPARKLING FELLOW</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>6</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2324,47 +3180,79 @@
           <t>10/2/4/5/3/2</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="K27" t="n">
-        <v>7</v>
-      </c>
-      <c r="L27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P27" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>5.5832</v>
-      </c>
-      <c r="R27" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="S27" t="n">
-        <v>7.2</v>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>5.5832</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
       </c>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>7</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="n">
-        <v>3</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2376,8 +3264,10 @@
           <t>CANDLELIGHT DINNER</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>10</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2394,47 +3284,79 @@
           <t>3/11/1/10/1/8</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="K28" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P28" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>5.418</v>
-      </c>
-      <c r="R28" t="n">
-        <v>10</v>
-      </c>
-      <c r="S28" t="n">
-        <v>8.5</v>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>5.418</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
       </c>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>7</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="n">
-        <v>4</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2446,8 +3368,10 @@
           <t>HORSEPOWER</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>2</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2464,47 +3388,79 @@
           <t>2/9/6/4/13/5</t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>4</v>
-      </c>
-      <c r="K29" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>10</v>
-      </c>
-      <c r="P29" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>5.411</v>
-      </c>
-      <c r="R29" t="n">
-        <v>10</v>
-      </c>
-      <c r="S29" t="n">
-        <v>8.5</v>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>5.411</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
       </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>8</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="n">
-        <v>1</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2516,8 +3472,10 @@
           <t>CHINA WIN</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>2</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2534,47 +3492,79 @@
           <t>3/2/1/1/2/6</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="K30" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N30" t="n">
-        <v>5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>6.785714285714286</v>
-      </c>
-      <c r="P30" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>6.2668</v>
-      </c>
-      <c r="R30" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.7</v>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>7.86</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>6.785714285714286</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>6.2668</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
       </c>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>8</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="n">
-        <v>2</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2586,8 +3576,10 @@
           <t>LIVEANDLETLIVE</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>3</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2604,47 +3596,79 @@
           <t>2/4/12/2/2/10</t>
         </is>
       </c>
-      <c r="J31" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="K31" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="L31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>5</v>
-      </c>
-      <c r="O31" t="n">
-        <v>10</v>
-      </c>
-      <c r="P31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>5.7407</v>
-      </c>
-      <c r="R31" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="S31" t="n">
-        <v>6.2</v>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>5.7407</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
       </c>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>8</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="n">
-        <v>3</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2656,8 +3680,10 @@
           <t>ACE WAR</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>11</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2674,47 +3700,79 @@
           <t>1/1/3/2/2/6</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="K32" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="L32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>5</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.642857142857143</v>
-      </c>
-      <c r="P32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>5.5421</v>
-      </c>
-      <c r="R32" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="S32" t="n">
-        <v>7.6</v>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>7.57</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>1.642857142857143</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>5.5421</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
       </c>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>8</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" t="n">
-        <v>4</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2726,8 +3784,10 @@
           <t>HIGHLAND RAHY</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>1</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2744,47 +3804,79 @@
           <t>5/9/5/11/7/2</t>
         </is>
       </c>
-      <c r="J33" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="K33" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>5</v>
-      </c>
-      <c r="O33" t="n">
-        <v>8.071428571428571</v>
-      </c>
-      <c r="P33" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>5.4811</v>
-      </c>
-      <c r="R33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="S33" t="n">
-        <v>8.1</v>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>4.62</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>8.071428571428571</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>5.4811</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
       </c>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>9</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="n">
-        <v>1</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2796,8 +3888,10 @@
           <t>AURIO</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>4</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2814,47 +3908,79 @@
           <t>1/4/4/2/1/2</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="K34" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>5</v>
-      </c>
-      <c r="O34" t="n">
-        <v>10</v>
-      </c>
-      <c r="P34" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>6.6276</v>
-      </c>
-      <c r="R34" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.7</v>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>8.57</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>6.6276</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
       </c>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>9</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="n">
-        <v>2</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2866,8 +3992,10 @@
           <t>LOVE TOGETHER</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>5</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2884,47 +4012,79 @@
           <t>7/8/3/1/6/2</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K35" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="L35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>5</v>
-      </c>
-      <c r="O35" t="n">
-        <v>8.875</v>
-      </c>
-      <c r="P35" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>6.0497</v>
-      </c>
-      <c r="R35" t="n">
-        <v>13</v>
-      </c>
-      <c r="S35" t="n">
-        <v>6.5</v>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>8.875</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>6.0497</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
       </c>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>9</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
-        <v>3</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2936,8 +4096,10 @@
           <t>PACKING GLORY</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>1</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2954,47 +4116,79 @@
           <t>5/3/3/2/5/1</t>
         </is>
       </c>
-      <c r="J36" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="K36" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>5</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1</v>
-      </c>
-      <c r="P36" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>5.9045</v>
-      </c>
-      <c r="R36" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="S36" t="n">
-        <v>7.5</v>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>5.9045</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
       </c>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>9</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="n">
-        <v>4</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3006,8 +4200,10 @@
           <t>MY DAY MY WAY</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>11</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3024,39 +4220,67 @@
           <t>1/1/10/2/8/1</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="K37" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="L37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N37" t="n">
-        <v>5</v>
-      </c>
-      <c r="O37" t="n">
-        <v>8.875</v>
-      </c>
-      <c r="P37" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>5.7823</v>
-      </c>
-      <c r="R37" t="n">
-        <v>10</v>
-      </c>
-      <c r="S37" t="n">
-        <v>8.5</v>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>6.62</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>8.875</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>5.7823</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
       </c>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3235,7 +4459,6 @@
           <t>3/2/1/1/2/6</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>7.86</v>
       </c>
@@ -3316,7 +4539,6 @@
           <t>2/4/12/2/2/10</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.29</v>
       </c>
@@ -3482,7 +4704,6 @@
           <t>5/9/5/11/7/2</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>4.62</v>
       </c>
@@ -3563,7 +4784,6 @@
           <t>7/1/11/2/9/5</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4.86</v>
       </c>
@@ -3644,7 +4864,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5</v>
       </c>
@@ -3725,7 +4944,6 @@
           <t>6/9/5/7/4/3</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5.38</v>
       </c>
@@ -3806,7 +5024,6 @@
           <t>5/4/2/14/14</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.53</v>
       </c>
@@ -3887,7 +5104,6 @@
           <t>3/5/10/13/5</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3.33</v>
       </c>
@@ -3968,7 +5184,6 @@
           <t>4/6/13/8/1/10</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>3.86</v>
       </c>
@@ -4049,7 +5264,6 @@
           <t>11/5/6/6/12/4</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>3.81</v>
       </c>
@@ -4130,7 +5344,6 @@
           <t>13/9/11/14/10/8</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.38</v>
       </c>
@@ -4342,7 +5555,6 @@
           <t>1/4/4/2/1/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.57</v>
       </c>
@@ -4423,7 +5635,6 @@
           <t>7/8/3/1/6/2</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.9</v>
       </c>
@@ -4504,7 +5715,6 @@
           <t>5/3/3/2/5/1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>7.9</v>
       </c>
@@ -4585,7 +5795,6 @@
           <t>1/1/10/2/8/1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>6.62</v>
       </c>
@@ -4666,7 +5875,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5</v>
       </c>
@@ -4747,7 +5955,6 @@
           <t>4/1/4/10/8/1</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5.62</v>
       </c>
@@ -4828,7 +6035,6 @@
           <t>2/5/1/8/9</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4.47</v>
       </c>
@@ -4909,7 +6115,6 @@
           <t>10/7/10/2/2/10</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>4.62</v>
       </c>
@@ -4990,7 +6195,6 @@
           <t>8/8/1/12/6/6</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>4</v>
       </c>
@@ -5071,7 +6275,6 @@
           <t>10/8/7/5/6/8</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>3.14</v>
       </c>
@@ -5152,7 +6355,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>5</v>
       </c>
@@ -5233,7 +6435,6 @@
           <t>7/5/6/7/6/8</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>3.29</v>
       </c>
@@ -5418,7 +6619,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>4</t>
@@ -5520,7 +6720,6 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>6</t>
@@ -5622,7 +6821,6 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>1</t>
@@ -5724,7 +6922,6 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>6</t>
@@ -5826,7 +7023,6 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>1</t>
@@ -5928,7 +7124,6 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>1</t>
@@ -6030,7 +7225,6 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>5</t>
@@ -6132,7 +7326,6 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>3</t>
@@ -6234,7 +7427,6 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>1</t>
@@ -6509,7 +7701,6 @@
           <t>8/4/6/2/7/3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>5.95</v>
       </c>
@@ -6590,7 +7781,6 @@
           <t>8/7/7/2/1/9</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.48</v>
       </c>
@@ -6671,7 +7861,6 @@
           <t>6/9/3/3/5/6</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.38</v>
       </c>
@@ -6752,7 +7941,6 @@
           <t>4/11/9/5/8/2</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>4.67</v>
       </c>
@@ -6833,7 +8021,6 @@
           <t>9/7/14/12/11/3</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>3.24</v>
       </c>
@@ -6914,7 +8101,6 @@
           <t>2/8/8/9/3/12</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>3.48</v>
       </c>
@@ -6995,7 +8181,6 @@
           <t>4/8/11/2/4/12</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4.05</v>
       </c>
@@ -7076,7 +8261,6 @@
           <t>13/7/12/12/5/11</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>2.14</v>
       </c>
@@ -7157,7 +8341,6 @@
           <t>11/8/11/13/9/9</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>1.62</v>
       </c>
@@ -7238,7 +8421,6 @@
           <t>12/8/10/12/9/9</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1.62</v>
       </c>
@@ -7319,7 +8501,6 @@
           <t>13/12/5/9/9/12</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2</v>
       </c>
@@ -7616,7 +8797,6 @@
           <t>2/4/8/5/1/3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>6.9</v>
       </c>
@@ -7697,7 +8877,6 @@
           <t>7/6/4/8/4/1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.05</v>
       </c>
@@ -7778,7 +8957,6 @@
           <t>3/12/2/1/12/5</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.33</v>
       </c>
@@ -7859,7 +9037,6 @@
           <t>7/5/2/3/6/8</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>4.95</v>
       </c>
@@ -7940,7 +9117,6 @@
           <t>3/9/1/9/6/7</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4.19</v>
       </c>
@@ -8021,7 +9197,6 @@
           <t>11/7/8/12/1/7</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4.05</v>
       </c>
@@ -8102,7 +9277,6 @@
           <t>9/10/5/10/14/4</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.05</v>
       </c>
@@ -8183,7 +9357,6 @@
           <t>1/10/12/5/10/6</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.05</v>
       </c>
@@ -8264,7 +9437,6 @@
           <t>11/12/3/5/10/11</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2.76</v>
       </c>
@@ -8345,7 +9517,6 @@
           <t>11/9/14/11/6/11</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1.81</v>
       </c>
@@ -8426,7 +9597,6 @@
           <t>10/11/5/13/13/9</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.86</v>
       </c>
@@ -8723,7 +9893,6 @@
           <t>9/2/4/7/2/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>7.38</v>
       </c>
@@ -8804,7 +9973,6 @@
           <t>8/9/14/1/2/1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>7.33</v>
       </c>
@@ -8885,7 +10053,6 @@
           <t>4/6/7/4/1/12</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>4.9</v>
       </c>
@@ -8966,7 +10133,6 @@
           <t>3/10/3/3/3/4</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>6.76</v>
       </c>
@@ -9047,7 +10213,6 @@
           <t>3/5/8/7/13/1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4.81</v>
       </c>
@@ -9128,7 +10293,6 @@
           <t>6/7</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>3.33</v>
       </c>
@@ -9209,7 +10373,6 @@
           <t>9/11/9/3/8/12</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>2.76</v>
       </c>
@@ -9290,7 +10453,6 @@
           <t>6/8/7/5/5/9</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.52</v>
       </c>
@@ -9371,7 +10533,6 @@
           <t>8/2/14/12/8/10</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2.05</v>
       </c>
@@ -9452,7 +10613,6 @@
           <t>10/6/11/6/9/14</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.1</v>
       </c>
@@ -9533,7 +10693,6 @@
           <t>13/12/10/9/12</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.27</v>
       </c>
@@ -9614,7 +10773,6 @@
           <t>6/9/8/7/10/10</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.76</v>
       </c>
@@ -9826,7 +10984,6 @@
           <t>2/9/3/4/3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>6.73</v>
       </c>
@@ -9907,7 +11064,6 @@
           <t>4/1/4/3/8/2</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.67</v>
       </c>
@@ -9988,7 +11144,6 @@
           <t>5/5/9/2/1/9</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.67</v>
       </c>
@@ -10069,7 +11224,6 @@
           <t>4/9/7/3</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.1</v>
       </c>
@@ -10150,7 +11304,6 @@
           <t>7/8/12/13/2/9</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>3.38</v>
       </c>
@@ -10316,7 +11469,6 @@
           <t>5/7</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.67</v>
       </c>
@@ -10397,7 +11549,6 @@
           <t>10/13/11/10/12</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>1</v>
       </c>
@@ -10478,7 +11629,6 @@
           <t>6/7/10/10</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>1.7</v>
       </c>
@@ -10559,7 +11709,6 @@
           <t>6/8/14</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1.83</v>
       </c>
@@ -10640,7 +11789,6 @@
           <t>10/10/14/14/11/9</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.29</v>
       </c>
@@ -10721,7 +11869,6 @@
           <t>10/11/12/14/7</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.67</v>
       </c>
@@ -10933,7 +12080,6 @@
           <t>2/2/1/2/4/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.710000000000001</v>
       </c>
@@ -11014,7 +12160,6 @@
           <t>14/5/14/8/1/2</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6</v>
       </c>
@@ -11095,7 +12240,6 @@
           <t>9/10/13/7/1/1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.14</v>
       </c>
@@ -11176,7 +12320,6 @@
           <t>7/1/3/3/2/11</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>6.19</v>
       </c>
@@ -11257,7 +12400,6 @@
           <t>8/9/3/9/3/1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>6.57</v>
       </c>
@@ -11338,7 +12480,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5</v>
       </c>
@@ -11504,7 +12645,6 @@
           <t>5/6/9/2/10/2</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>5.43</v>
       </c>
@@ -11585,7 +12725,6 @@
           <t>8/4/5/3/4/8</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>4.9</v>
       </c>
@@ -11666,7 +12805,6 @@
           <t>8/6/3/5/8/7</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>3.9</v>
       </c>
@@ -11747,7 +12885,6 @@
           <t>4/6/5/5/5/8</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>4.1</v>
       </c>
@@ -11828,7 +12965,6 @@
           <t>11/10/8/1/11/11</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2.86</v>
       </c>
@@ -12040,7 +13176,6 @@
           <t>10/2/3/4/2/5</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>6.76</v>
       </c>
@@ -12121,7 +13256,6 @@
           <t>4/3/9/4/3/6</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.52</v>
       </c>
@@ -12202,7 +13336,6 @@
           <t>4/5/8/5/7/1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.57</v>
       </c>
@@ -12283,7 +13416,6 @@
           <t>2/2/5/4/5/6</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.48</v>
       </c>
@@ -12364,7 +13496,6 @@
           <t>7/3/6/4/4/4</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5.76</v>
       </c>
@@ -12445,7 +13576,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5</v>
       </c>
@@ -12526,7 +13656,6 @@
           <t>12/4</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4.33</v>
       </c>
@@ -12607,7 +13736,6 @@
           <t>5/3/6/5/6/12</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.76</v>
       </c>
@@ -12688,7 +13816,6 @@
           <t>11/11/9/4</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3.3</v>
       </c>
@@ -12769,7 +13896,6 @@
           <t>6/11/6/10/12</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1.8</v>
       </c>
@@ -12850,7 +13976,6 @@
           <t>11/11</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1</v>
       </c>
@@ -13147,7 +14272,6 @@
           <t>1/1/3/1/2/3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.9</v>
       </c>
@@ -13228,7 +14352,6 @@
           <t>10/2/4/5/3/2</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>7.19</v>
       </c>
@@ -13309,7 +14432,6 @@
           <t>3/11/1/10/1/8</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.05</v>
       </c>
@@ -13390,7 +14512,6 @@
           <t>2/9/6/4/13/5</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>4</v>
       </c>
@@ -13471,7 +14592,6 @@
           <t>4/7/8/2</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5.4</v>
       </c>
@@ -13552,7 +14672,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5</v>
       </c>
@@ -13633,7 +14752,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5</v>
       </c>
@@ -13714,7 +14832,6 @@
           <t>1/1/3/11/7/5</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>4.9</v>
       </c>
@@ -13795,7 +14912,6 @@
           <t>9/9/8/12/1/12</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3.43</v>
       </c>
@@ -13876,7 +14992,6 @@
           <t>12/6/10/7/8/3</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>3.9</v>
       </c>
@@ -13957,7 +15072,6 @@
           <t>7/10/8/11/9/13</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.48</v>
       </c>
@@ -14038,7 +15152,6 @@
           <t>11/12</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1</v>
       </c>
